--- a/public/templates/sru-three-sixty-template.xlsx
+++ b/public/templates/sru-three-sixty-template.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="84">
   <si>
     <t>قالب تقييم 360 — ملف إكسل بأربع أوراق عمل، كل ورقة تقابل جدول كتالوج مشترك بين كل الدورات:</t>
   </si>
@@ -53,6 +53,12 @@
     <t xml:space="preserve">   reverse_scored = TRUE للعبارات المصاغة سلبًا (يُعكس ترتيبها تلقائيًا قبل الاحتساب).</t>
   </si>
   <si>
+    <t xml:space="preserve">   behavioral_level: basic أو practitioner أو advanced أو professional — يُظهر العبارة فقط لموظف تتطلب وظيفته هذا المستوى من الجدارة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   (المستوى الافتراضي عند غياب تحديد صريح في مسمى الموظف الوظيفي هو practitioner). اتركه فارغًا لعبارة تُعرض بغض النظر عن المستوى (مثل النص الحر).</t>
+  </si>
+  <si>
     <t>القيم المنطقية (TRUE/FALSE) تقبل أيضًا: 1/0، نعم/لا، صح.</t>
   </si>
   <si>
@@ -224,6 +230,9 @@
     <t>display_order</t>
   </si>
   <si>
+    <t>behavioral_level</t>
+  </si>
+  <si>
     <t>comm_1</t>
   </si>
   <si>
@@ -236,10 +245,16 @@
     <t>self,supervisor,peer,subordinate</t>
   </si>
   <si>
+    <t>practitioner</t>
+  </si>
+  <si>
     <t>lead_2</t>
   </si>
   <si>
     <t>يتجنب اتخاذ القرارات الصعبة عند الحاجة.</t>
+  </si>
+  <si>
+    <t>advanced</t>
   </si>
   <si>
     <t>open_1</t>
@@ -258,7 +273,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -268,27 +283,14 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF7A7A7A"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7E0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -303,17 +305,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -653,100 +647,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>1</v>
+      <c r="A16" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>12</v>
+      <c r="A17" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>13</v>
+      <c r="A18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -763,123 +767,123 @@
     <col min="1" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="5">
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="E2" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5">
         <v>3</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6">
         <v>4</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7">
         <v>5</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>25</v>
+      <c r="E7" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -896,119 +900,119 @@
     <col min="1" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="5">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="5">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="5">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4">
         <v>50</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>6</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="5">
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>6</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>25</v>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1025,71 +1029,71 @@
     <col min="1" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3">
         <v>35</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="5">
-        <v>40</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="5">
-        <v>35</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="5">
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4">
         <v>25</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1101,126 +1105,138 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="9" width="22" customWidth="1"/>
+    <col min="1" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="3" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="H1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="J1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="D2" t="s">
         <v>74</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="5">
+      <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
+      <c r="J3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>3</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
